--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126125633</v>
+        <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421861</v>
+        <v>421340</v>
       </c>
       <c r="R2" t="n">
-        <v>6962444</v>
+        <v>6962923</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125633</t>
+          <t>https://artportalen.se/Sighting/136815130</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126125649</v>
+        <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>92382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,45 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421727</v>
+        <v>421361</v>
       </c>
       <c r="R3" t="n">
-        <v>6962650</v>
+        <v>6962635</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125649</t>
+          <t>https://artportalen.se/Sighting/136814291</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126125669</v>
+        <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,45 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421399</v>
+        <v>421332</v>
       </c>
       <c r="R4" t="n">
-        <v>6962782</v>
+        <v>6962842</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,27 +969,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125669</t>
+          <t>https://artportalen.se/Sighting/136815483</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126125710</v>
+        <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>93421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,45 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421509</v>
+        <v>421299</v>
       </c>
       <c r="R5" t="n">
-        <v>6962716</v>
+        <v>6962857</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,73 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125710</t>
+          <t>https://artportalen.se/Sighting/136815456</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348511</v>
+        <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421432</v>
+        <v>421334</v>
       </c>
       <c r="R6" t="n">
-        <v>6962635</v>
+        <v>6962668</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,65 +1173,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348511</t>
+          <t>https://artportalen.se/Sighting/136814545</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348533</v>
+        <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421761</v>
+        <v>421373</v>
       </c>
       <c r="R7" t="n">
-        <v>6962549</v>
+        <v>6962696</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,65 +1275,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348533</t>
+          <t>https://artportalen.se/Sighting/136814598</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348534</v>
+        <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421772</v>
+        <v>421264</v>
       </c>
       <c r="R8" t="n">
-        <v>6962583</v>
+        <v>6962982</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,65 +1377,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348534</t>
+          <t>https://artportalen.se/Sighting/136815249</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348535</v>
+        <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421837</v>
+        <v>421379</v>
       </c>
       <c r="R9" t="n">
-        <v>6962687</v>
+        <v>6962768</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,17 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,24 +1479,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348535</t>
+          <t>https://artportalen.se/Sighting/136815544</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348536</v>
+        <v>126125633</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1585,19 +1525,27 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421629</v>
+        <v>421861</v>
       </c>
       <c r="R10" t="n">
-        <v>6962773</v>
+        <v>6962444</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,17 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,24 +1589,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348536</t>
+          <t>https://artportalen.se/Sighting/126125633</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348537</v>
+        <v>126125649</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1692,19 +1635,27 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421606</v>
+        <v>421727</v>
       </c>
       <c r="R11" t="n">
-        <v>6962786</v>
+        <v>6962650</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,17 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,24 +1699,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348537</t>
+          <t>https://artportalen.se/Sighting/126125649</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348538</v>
+        <v>126125669</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1799,19 +1745,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421606</v>
+        <v>421399</v>
       </c>
       <c r="R12" t="n">
-        <v>6962795</v>
+        <v>6962782</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,17 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,24 +1809,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348538</t>
+          <t>https://artportalen.se/Sighting/126125669</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126348540</v>
+        <v>126125710</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -1906,19 +1855,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421420</v>
+        <v>421509</v>
       </c>
       <c r="R13" t="n">
-        <v>6962900</v>
+        <v>6962716</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,17 +1899,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,24 +1919,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348540</t>
+          <t>https://artportalen.se/Sighting/126125710</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126348541</v>
+        <v>126348511</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -2013,16 +1965,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421342</v>
+        <v>421432</v>
       </c>
       <c r="R14" t="n">
-        <v>6962830</v>
+        <v>6962635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,13 +2045,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348541</t>
+          <t>https://artportalen.se/Sighting/126348511</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126348542</v>
+        <v>126348533</v>
       </c>
       <c r="B15" t="n">
         <v>57953</v>
@@ -2126,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421390</v>
+        <v>421761</v>
       </c>
       <c r="R15" t="n">
-        <v>6962623</v>
+        <v>6962549</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,16 +2152,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348542</t>
+          <t>https://artportalen.se/Sighting/126348533</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126133773</v>
+        <v>126348534</v>
       </c>
       <c r="B16" t="n">
-        <v>79917</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,40 +2169,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421831</v>
+        <v>421772</v>
       </c>
       <c r="R16" t="n">
-        <v>6962414</v>
+        <v>6962583</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,12 +2223,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,23 +2242,1746 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348534</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126348535</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421837</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6962687</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348535</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126348536</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421629</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6962773</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348536</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126348537</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421606</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6962786</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348537</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126348538</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421606</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6962795</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348538</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126348540</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421420</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6962900</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348540</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126348541</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421342</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6962830</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348541</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126348542</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421390</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962623</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348542</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136814581</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421348</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962696</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814581</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136814772</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Över Dammtjärn, Abborrsjön,Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421421</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6962722</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814772</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136815296</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421191</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6962978</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815296</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136815491</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421341</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6962858</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815491</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136815177</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>421338</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6962929</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815177</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136815093</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>421388</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6962889</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815093</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136815233</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>421301</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6962968</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815233</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136815435</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>421230</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6962885</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815435</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126133773</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6962414</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126133773</t>
         </is>
@@ -2319,6 +4004,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3984,6 +3984,109 @@
       <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126133773</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136917941</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>421327</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6962725</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917941</t>
         </is>
       </c>
     </row>
@@ -4020,6 +4123,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136814581</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>136814772</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>136815296</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136815491</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136815177</v>
       </c>
       <c r="B28" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136815093</v>
       </c>
       <c r="B29" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136815233</v>
       </c>
       <c r="B30" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136814581</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>136814772</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>136815296</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>136815491</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136815177</v>
       </c>
       <c r="B28" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136815093</v>
       </c>
       <c r="B29" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136815233</v>
       </c>
       <c r="B30" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -3043,11 +3043,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
@@ -3155,11 +3151,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Över Dammtjärn, Abborrsjön,Storsjö, Hjd</t>
@@ -3267,11 +3259,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
@@ -3379,11 +3367,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
@@ -3495,11 +3479,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136814581</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136814772</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136815296</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>136815491</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136815177</v>
       </c>
       <c r="B28" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>136815093</v>
       </c>
       <c r="B29" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136815233</v>
       </c>
       <c r="B30" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136814581</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136814772</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136815296</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>136815491</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136815177</v>
       </c>
       <c r="B28" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>136815093</v>
       </c>
       <c r="B29" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136815233</v>
       </c>
       <c r="B30" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815130</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136814291</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136815483</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136815456</v>
       </c>
       <c r="B5" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136814545</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136814598</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136815249</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136815544</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136814581</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>136814772</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136815296</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>136815491</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136815177</v>
       </c>
       <c r="B28" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>136815093</v>
       </c>
       <c r="B29" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136815233</v>
       </c>
       <c r="B30" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>136815435</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -3972,7 +3972,7 @@
         <v>136917941</v>
       </c>
       <c r="B33" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
